--- a/btp/Curing/V1 11-37-56-875/load_running_moulds.xlsx
+++ b/btp/Curing/V1 11-37-56-875/load_running_moulds.xlsx
@@ -537,11 +537,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['GC08', 'GC15']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>539</v>
+        <v>2552</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -560,11 +560,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['GC10', 'GC16']</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>323</v>
+        <v>2352</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -583,11 +583,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['GC07', 'GC09']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2169</v>
+        <v>1165</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -601,16 +601,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1D25214012008QXPCT</t>
+          <t>1325216612077TUSP0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['GC12', 'GC05']</t>
+          <t>['MK1', 'MK2']</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -629,11 +629,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['GC03', 'GC06']</t>
+          <t>['GC04', 'GC05']</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1901</v>
+        <v>968</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -652,11 +652,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['HM05', 'HM07']</t>
+          <t>['HM10', 'HM15']</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>489</v>
+        <v>800</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>649</v>
+        <v>296</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2846</v>
+        <v>2400</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>2523</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -739,16 +739,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1325215813079TUNE5</t>
+          <t>1325218614088TTMX0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['GC04', 'GC07']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>714</v>
+        <v>1191</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -762,16 +762,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1325215514075TUNE0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['GC02', 'GC10']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>869</v>
+        <v>897</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -790,14 +790,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['0']</t>
+          <t>['GC01', 'GC02']</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2325</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -808,16 +808,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1325215813079TUNE5</t>
+          <t>1325215514075TUNE0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['GC09', 'GC10']</t>
+          <t>['GC01', 'GC02']</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1487</v>
+        <v>897</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -831,16 +831,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1325215513073TUNE0</t>
+          <t>1325215813079TUNE5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['GC02', 'GC06']</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -859,11 +859,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['HM08', 'HM16']</t>
+          <t>['HM05', 'HM07']</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>877</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>624</v>
+        <v>272</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -900,16 +900,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1325215813079TUNE5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['HM09', 'HM22']</t>
+          <t>['GC03', 'GC08']</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>877</v>
+        <v>2156</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -923,16 +923,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1D25214012008QXPCT</t>
+          <t>1D25215013008SXC10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['GC08', 'GC15']</t>
+          <t>['SM01', 'SM02']</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1440</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -951,11 +951,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['HM14', 'HM25']</t>
+          <t>['HM16', 'HM31']</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>878</v>
+        <v>133</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>693</v>
+        <v>261</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1325218614088TTMX0</t>
+          <t>1325218316083HURL0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>954</v>
+        <v>529</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -1015,16 +1015,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1325214812074TUHL0</t>
+          <t>1D25114012008QXPC0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['HMI08', 'HMI11']</t>
+          <t>['GC11', 'GC14']</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1998</v>
+        <v>592</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1325215514075TUNE0</t>
+          <t>1325214617107MSXT0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['HM01', 'HM02']</t>
+          <t>['SX01', 'SX02']</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>703</v>
+        <v>597</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -1066,11 +1066,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['SX02', 'SX03']</t>
+          <t>['AL01', 'SX03']</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2201</v>
+        <v>660</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['GC01', 'GC05']</t>
+          <t>['HMI08', 'HMI10']</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1144</v>
+        <v>1355</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1107,16 +1107,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1D25214012008QXPCT</t>
+          <t>1325220416092HRHT0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['GC10', 'GC16']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1225</v>
+        <v>695</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1D25214012008QXPCT</t>
+          <t>1D25114012008QXPC0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2658</v>
+        <v>444</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['HMI10', 'HM12']</t>
+          <t>['GC01', 'GC02']</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>116</v>
+        <v>1337</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['HM01', 'HM02']</t>
+          <t>['GC03', 'GC06']</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>786</v>
+        <v>934</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -1199,16 +1199,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1325218316083HURL0</t>
+          <t>1325219416089VRHE0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['HM01', 'HM02']</t>
+          <t>['HMI05', 'HMI09']</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>481</v>
+        <v>733</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -1222,16 +1222,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1225219Z15008SXC11</t>
+          <t>1225219Z15008SXC10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['CGC02', 'HM04']</t>
+          <t>['GC01', 'GC02']</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>77</v>
+        <v>1129</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1245,16 +1245,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1D25216814008QXPC0</t>
+          <t>1D25218014010RXPCT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['GC08', 'GC10']</t>
+          <t>['HM04', 'HM06']</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709</v>
+        <v>903</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>516</v>
+        <v>461</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -1296,11 +1296,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['HMI03', 'HMI04']</t>
+          <t>['HMI0', 'HMI0']</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>534</v>
+        <v>453</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -1314,16 +1314,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1225219Z15008SXC11</t>
+          <t>1225219Z15008SXC10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['HM05', 'HM06']</t>
+          <t>['GC03', 'GC04']</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>748</v>
+        <v>965</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1337,16 +1337,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1325218614088TTMX0</t>
+          <t>1D25218014010RXPCT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['HMI01', 'HMI02']</t>
+          <t>['HM05', 'HM08']</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>811</v>
+        <v>602</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1606</v>
+        <v>928</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['HMI01', 'HMI02']</t>
+          <t>['HMI0', 'HMI0']</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>222</v>
+        <v>434</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1406,16 +1406,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1325221417096HURL0</t>
+          <t>1D25215013008SXC10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['GC05', 'GC06']</t>
+          <t>['HMI0', 'HM32']</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>1886</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1429,16 +1429,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1325221318095HURL0</t>
+          <t>1325221417096HURL0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['GC01', 'GC02']</t>
+          <t>['GC03', 'GC04']</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1486</v>
+        <v>75</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -1452,16 +1452,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1225219Z15008SXC11</t>
+          <t>1225219Z15008SXC10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['CGC01', 'HM03']</t>
+          <t>['CHM01', 'CHM02']</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
@@ -1475,16 +1475,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1D25218014010RXPCT</t>
+          <t>1325218614088TTMX0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['HM02', 'HM03']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2072</v>
+        <v>1255</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -1498,16 +1498,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1D25218014010RXPCT</t>
+          <t>1D25216814008QXPC0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['HM04', 'HM06']</t>
+          <t>['GC06', 'GC09']</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1122</v>
+        <v>527</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -1521,16 +1521,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1225219Z15008SXC11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['GC06', 'GC07']</t>
+          <t>['HM05', 'HM06']</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -1544,16 +1544,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1325219416089VRHE0</t>
+          <t>1325217515084HURL2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['HMI07', 'HMI07']</t>
+          <t>['HMI03', 'HMI06']</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>379</v>
+        <v>1348</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['GC03', 'GC04']</t>
+          <t>['GC05', 'GC06']</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1642</v>
+        <v>2753</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1325221317094VURL1</t>
+          <t>1325225518111HRHB0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>99</v>
+        <v>1522</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1618,11 +1618,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['HM13', 'HM28']</t>
+          <t>['HM25', 'HM27']</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2387</v>
+        <v>2899</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['HMI01', 'HMI02']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2073</v>
+        <v>2696</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -1659,16 +1659,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1325218614088TTMX0</t>
+          <t>1D25216814008QXPC0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['GC04', 'GC07']</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>857</v>
+        <v>979</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1687,11 +1687,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['HM29', 'HM30']</t>
+          <t>['GC06', 'GC07']</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2720</v>
+        <v>826</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -1705,16 +1705,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1325219515091HURL2</t>
+          <t>1325217515084HURL2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['HMI06', 'HMI07']</t>
+          <t>['HMI01', 'HMI07']</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2057</v>
+        <v>1392</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -1733,11 +1733,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['HM11', 'HM27']</t>
+          <t>['HM08', 'HM23']</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>887</v>
+        <v>1682</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -1756,11 +1756,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['GC09', 'HM26']</t>
+          <t>['HM29', 'HM30']</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1327</v>
+        <v>1977</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['HM10', 'HM15']</t>
+          <t>['GC04', 'GC05']</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1328</v>
+        <v>2637</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1797,16 +1797,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1325217515084HURL2</t>
+          <t>1D25215013008SXC10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['HMI04', 'HMI08']</t>
+          <t>['GC08', 'GC10']</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>116</v>
+        <v>999</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -1820,16 +1820,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1325225518111HRHB0</t>
+          <t>1325217515084HURL2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['HM05', 'HM06']</t>
+          <t>['HMI0', 'HMI0']</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1364</v>
+        <v>883</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -1843,16 +1843,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1325217515084HURL2</t>
+          <t>1325225518111HRHB0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['HMI02', 'HMI06']</t>
+          <t>['HM05', 'HM06']</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1480</v>
+        <v>1281</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
@@ -1866,16 +1866,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1325221417096HURL0</t>
+          <t>1325219416089VRHE0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['HM24', 'HM27']</t>
+          <t>['HMI07', 'HMI08']</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>73</v>
+        <v>501</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
@@ -1889,16 +1889,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1D25216814008QXPC0</t>
+          <t>1325221417096HURL0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['GC03', 'GC05']</t>
+          <t>['HMI01', 'HMI02']</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
@@ -1912,16 +1912,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1325215813079TUNE5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['HM17', 'HM31']</t>
+          <t>['GC04', 'GC10']</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2844</v>
+        <v>1866</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['HMI05', 'HMI08']</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2039</v>
+        <v>81</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>573</v>
+        <v>693</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['HMI05', 'HMI18']</t>
+          <t>['HMI08', 'HMI12']</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>212</v>
+        <v>2923</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -2009,11 +2009,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['GC04', 'GC05']</t>
+          <t>['HM13', 'HM28']</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>506</v>
+        <v>946</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['GC01', 'HM21']</t>
+          <t>['GC09', 'HM26']</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>520</v>
+        <v>866</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1325220416092HRHT0</t>
+          <t>1325225518111HRHB0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>498</v>
+        <v>434</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1325221318095HURL0</t>
+          <t>1325225518111HRHB0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['HM02', 'HMI17']</t>
+          <t>['HMI03', 'HMI04']</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>282</v>
+        <v>1085</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -2101,11 +2101,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['HM22', 'HM26']</t>
+          <t>['HM20', 'HM35']</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1217</v>
+        <v>2329</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1325219515091HURL2</t>
+          <t>1325217515084HURL2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>211</v>
+        <v>1088</v>
       </c>
       <c r="E74" t="n">
         <v>2</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['HM14', 'HM20']</t>
+          <t>['HM14', 'HM32']</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2212</v>
+        <v>1140</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['HMI0', 'HMI0']</t>
+          <t>['HM25', 'HM34']</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>2810</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1325225518111HRHB0</t>
+          <t>1325221417096HURL0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['HM03', 'HM04']</t>
+          <t>['HM18', 'HM26']</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1910</v>
+        <v>40</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -2216,11 +2216,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['HM04', 'HM32']</t>
+          <t>['HM17', 'HM21']</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>151</v>
+        <v>1779</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -2239,11 +2239,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['HM12', 'GC03']</t>
+          <t>['HM11', 'HM14']</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>421</v>
+        <v>2019</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -2257,16 +2257,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1D25218014010RXPCT</t>
+          <t>1325223616109SELZ0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['HM01', 'MK07']</t>
+          <t>['SY04', 'SY11']</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2093</v>
+        <v>165</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -2280,16 +2280,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1325221318095HURL0</t>
+          <t>1D25216814008QXPC0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['HMI13', 'HMI14']</t>
+          <t>['GC03', 'GC05']</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -2303,16 +2303,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1325221417096HURL0</t>
+          <t>1225219Z15008SXC11</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['HM16', 'HM32']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2875</v>
+        <v>371</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['HM01', 'HM02']</t>
+          <t>['GC01', 'HM03']</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>807</v>
+        <v>203</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -2354,11 +2354,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['HM01', 'HMI09']</t>
+          <t>['HMI01', 'HMI17']</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2848</v>
+        <v>72</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -2372,16 +2372,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1D25216814008QXPC0</t>
+          <t>1325221217095VUX10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['GC09', 'GC06']</t>
+          <t>['HM-01', 'HM-02']</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1466</v>
+        <v>255</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -2395,16 +2395,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1325222517102HRHT0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['GC08', 'HM23']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2573</v>
+        <v>291</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['HM01', 'HMI07']</t>
+          <t>['HMI07', 'HMI16']</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>319</v>
+        <v>2955</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -2441,16 +2441,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1325218316083HURL0</t>
+          <t>1325221416095VURP0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['HMI01', 'HMI02']</t>
+          <t>['HM01', 'HM02']</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>496</v>
+        <v>63</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2346</v>
+        <v>1394</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
@@ -2487,16 +2487,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1325217515084HURL2</t>
+          <t>1325219515091HURL2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['HMI01', 'HMI07']</t>
+          <t>['HM03', 'HM04']</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1971</v>
+        <v>1238</v>
       </c>
       <c r="E90" t="n">
         <v>2</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1D25215013008SXC10</t>
+          <t>1D25214012008QXPCT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
